--- a/不動産賃貸管理会社リスト_千葉_茨城_埼玉_2026.xlsx
+++ b/不動産賃貸管理会社リスト_千葉_茨城_埼玉_2026.xlsx
@@ -13,9 +13,9 @@
     <sheet name="埼玉県" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'千葉県'!$A$1:$H$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'茨城県'!$A$1:$H$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'埼玉県'!$A$1:$H$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'千葉県'!$A$1:$H$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'茨城県'!$A$1:$H$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'埼玉県'!$A$1:$H$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -566,7 +566,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・建設会社/工務店をグループ・併設に持つ不動産会社（例：三共土地建物＝三共矢崎建設、桂不動産＝建築土木、太陽ハウス＝建築部門 等）</t>
+          <t xml:space="preserve">  ・建設会社/工務店をグループ・併設に持つ不動産会社（例：三共土地建物＝三共矢崎建設、桂不動産＝建築土木、太陽ハウス＝建築部門、GMC＝一級建築士事務所 等）</t>
         </is>
       </c>
     </row>
@@ -607,59 +607,121 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・協力会社募集欄：公式サイトに「協力会社/協力業者/職人募集」ページがあるか。</t>
+          <t xml:space="preserve">  ・確度：高=賃貸管理+リフォーム+建設系グループ無しを確認 / 中=おおむね該当 / 低=該当だが管理規模やリフォーム部の体制に要確認点あり</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ※本調査は検索ベースのため大半は「要確認（公式HP）」。直接確認の追加調査が可能です。</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ・確度：高=賃貸管理+リフォーム+建設系グループ無しを確認 / 中=おおむね該当 / 低=該当だが管理規模やリフォーム部の体制に要確認点あり</t>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>■ ファクトチェック実施済み（2026-06-10）— 主な修正</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・柏ホーム TEL 04-7144-3661（旧データの番号は誤りを修正）</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>■ 注意</t>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・丸一土地建物 TEL 043-224-6561 / 松堀不動産 住所=東松山市箭弓町2-3-2・TEL 0493-24-1111</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・電話番号「要確認」は検索で番号が特定できなかった社（公式HPに掲載あり）。</t>
+          <t xml:space="preserve">  ・大みか不動産 TEL 0294-53-5878 / 一誠商事 TEL 029-852-6611 / ワンステップハウス 大宮区桜木町1-1-11・048-650-3100</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・吉田不動産は本社が大宮(埼玉)・管理の主力は市川/船橋等(千葉)のため埼玉に収録。</t>
+          <t xml:space="preserve">  ・吉田不動産＝本社は千葉県市川市南行徳(東西線地盤)と判明し【埼玉→千葉】へ訂正。大宮の同名社は別法人(土地分譲)で対象外</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・社数：千葉17 / 茨城17 / 埼玉15（条件を満たす地場企業を優先。20社/県への増補・協力会社募集欄の精査も対応可能）</t>
+          <t xml:space="preserve">  ・GMC（結城）＝実体は一級建築士事務所(建築設計・施工)のため除外</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ・調査日：2026-06-10</t>
+      <c r="A27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>■ 協力会社募集欄について（重要）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・各社名で「協力会社/協力業者/職人募集」を個別に検索確認（主要〜中堅31社）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・公開の募集ページが確認できたのは【サカイ・エージェンシー(熊谷)】1社のみ → https://sakai-ag.com/partner/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・他社は公開募集ページが無く「無」。＝Webフォームではなく直接打診(電話/訪問)が必要、という結論。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・吉岡地所(松戸)はリフォームを外部の協力会社へ発注する運用のため、直接営業の好機。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>■ 注意</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・電話番号「要確認」は公式番号を特定できなかった社（公式HPに掲載あり）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・社数：千葉18 / 茨城16 / 埼玉14（計48社／条件を満たす地場企業を優先。埼玉の増補・追加調査も可能）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・調査日：2026-06-10（検索ベース。最終判断は各社公式HP/直接確認を推奨）</t>
         </is>
       </c>
     </row>
@@ -674,7 +736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -755,7 +817,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（自社HPに募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
@@ -795,7 +857,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（自社HPに募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
@@ -815,27 +877,27 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>フーサワ商事株式会社</t>
+          <t>吉田不動産株式会社</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>〒277-0005 千葉県柏市柏2-3-1</t>
+          <t>〒272-0145 千葉県市川市南行徳1-22-29(本社)</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>04-7163-2230</t>
+          <t>047-395-5001</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>https://www.2230.jp/</t>
+          <t>https://www.yoshida-re.co.jp/</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（自社HPに募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -845,7 +907,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>柏で創業110年の老舗地場。賃貸管理・賃貸仲介・売買が柱+リフォーム・メンテ・退去クリーニング・24時間対応</t>
+          <t>1983設立・市川本社の地域密着(東西線:市川/船橋/浦安/松戸)。賃貸仲介・賃貸管理(約4,500〜7,000戸)・原状回復/大規模修繕・リフォーム費分割施工・駐車場約2,400台。建設系グループなし。※大宮の同名「吉田不動産」は別会社(土地分譲)</t>
         </is>
       </c>
     </row>
@@ -855,27 +917,27 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>株式会社明日香ホーム</t>
+          <t>フーサワ商事株式会社</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>〒263-0043 千葉県千葉市稲毛区小仲台2-13-1</t>
+          <t>〒277-0005 千葉県柏市柏2-3-1</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>043-256-5661</t>
+          <t>04-7163-2230</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>https://www.asuka-h.com/</t>
+          <t>https://www.2230.jp/</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（自社HPに募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -885,7 +947,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>1970創業・千葉市稲毛の賃貸管理特化。空室対策・古い物件のリノベーションに注力。全宅管理会員</t>
+          <t>柏で創業110年の老舗地場。賃貸管理・賃貸仲介・売買が柱+リフォーム・メンテ・退去クリーニング・24時間対応</t>
         </is>
       </c>
     </row>
@@ -895,37 +957,37 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>株式会社柏ホーム</t>
+          <t>株式会社明日香ホーム</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>千葉県柏市末広町(柏駅西口)</t>
+          <t>〒263-0043 千葉県千葉市稲毛区小仲台2-13-1</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>04-7145-1021</t>
+          <t>043-256-5661</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>https://www.kashiwa-home.co.jp/</t>
+          <t>https://www.asuka-h.com/</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>無（自社HPに募集ページ確認できず）</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>創業50年超。賃貸募集・管理+リフォーム改修工事。柏・流山・野田</t>
+          <t>1970創業・千葉市稲毛の賃貸管理特化。空室対策・古い物件のリノベーションに注力。全宅管理会員</t>
         </is>
       </c>
     </row>
@@ -935,27 +997,27 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>株式会社市川ビルサービス</t>
+          <t>株式会社柏ホーム</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>〒272-0106 千葉県市川市伊勢宿2-14</t>
+          <t>千葉県柏市末広町(柏駅西口)</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>047-358-7917</t>
+          <t>04-7144-3661</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>https://www.icbs.co.jp/</t>
+          <t>https://www.kashiwa-home.co.jp/</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（自社HPに募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -965,7 +1027,7 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>市川・船橋の賃貸管理主体+リフォーム各種工事(内外装)。JAいちかわ指定管理。社内に建築請負あり</t>
+          <t>創業1971年・柏駅前50年超・入居率98%。創業50年超。賃貸募集・管理+リフォーム改修工事。柏・流山・野田</t>
         </is>
       </c>
     </row>
@@ -975,27 +1037,27 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>有限会社東光不動産</t>
+          <t>株式会社市川ビルサービス</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>千葉県習志野市実籾3-1-6</t>
+          <t>〒272-0106 千葉県市川市伊勢宿2-14</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>047-472-0228</t>
+          <t>047-358-7917</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>https://toko-f.co.jp/</t>
+          <t>https://www.icbs.co.jp/</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（自社HPに募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1005,7 +1067,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>昭和39年開業。賃貸管理+建物管理・リフォーム・修繕計画。地域密着の街の不動産</t>
+          <t>市川・船橋の賃貸管理主体+リフォーム各種工事(内外装)。JAいちかわ指定管理。社内に建築請負あり</t>
         </is>
       </c>
     </row>
@@ -1015,27 +1077,27 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>株式会社京葉恒産</t>
+          <t>有限会社東光不動産</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>千葉県柏市中央1-3-30</t>
+          <t>千葉県習志野市実籾3-1-6</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>04-7166-8686</t>
+          <t>047-472-0228</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>https://www.keiyokosan.co.jp/</t>
+          <t>https://toko-f.co.jp/</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（公開募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
@@ -1045,7 +1107,7 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>賃貸・売買・賃貸管理・リフォーム・宅地開発。テナント賃貸に強い</t>
+          <t>昭和39年開業。賃貸管理+建物管理・リフォーム・修繕計画。地域密着の街の不動産</t>
         </is>
       </c>
     </row>
@@ -1055,27 +1117,27 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>大里綜合管理株式会社</t>
+          <t>株式会社京葉恒産</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>〒299-3236 千葉県大網白里市みやこ野2-3-1</t>
+          <t>千葉県柏市中央1-3-30</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>0475-72-3473</t>
+          <t>04-7166-8686</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>https://www.ohsato.co.jp/</t>
+          <t>https://www.keiyokosan.co.jp/</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（自社HPに募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -1085,7 +1147,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>大網白里の地域密着総合不動産(全国的に有名)。空き地管理・賃貸・売買・リフォーム。新築/建築工事も手がける点は要確認</t>
+          <t>賃貸・売買・賃貸管理・リフォーム・宅地開発。テナント賃貸に強い</t>
         </is>
       </c>
     </row>
@@ -1095,27 +1157,27 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>株式会社エヴァー</t>
+          <t>大里綜合管理株式会社</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>〒273-0005 千葉県船橋市本町7-14-1 天沼パークサイド1F</t>
+          <t>〒299-3236 千葉県大網白里市みやこ野2-3-1</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>047-421-0600</t>
+          <t>0475-72-3473</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>https://www.e-ever.co.jp/</t>
+          <t>https://www.ohsato.co.jp/</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（自社HPに募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -1125,7 +1187,7 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>船橋の地域密着。賃貸仲介・賃貸管理を柱に売買+建物修繕・リフォーム対応・24時間管理</t>
+          <t>大網白里の地域密着総合不動産(全国的に有名)。空き地管理・賃貸・売買・リフォーム。新築/建築工事も手がける点は要確認</t>
         </is>
       </c>
     </row>
@@ -1135,27 +1197,27 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>株式会社R-NEXT(アールネクスト)</t>
+          <t>株式会社エヴァー</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>〒277-0005 千葉県柏市柏2-8-17</t>
+          <t>〒273-0005 千葉県船橋市本町7-14-1 天沼パークサイド1F</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>04-7192-6791</t>
+          <t>047-421-0600</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>http://r-kashiwa.co.jp/</t>
+          <t>https://www.e-ever.co.jp/</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（公開募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1165,7 +1227,7 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>柏の地域密着。賃貸・売買・賃貸不動産管理・リフォーム・便利屋。内装リフォーム自社対応</t>
+          <t>船橋の地域密着。賃貸仲介・賃貸管理を柱に売買+建物修繕・リフォーム対応・24時間管理</t>
         </is>
       </c>
     </row>
@@ -1175,27 +1237,27 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>株式会社第一ホーム佐倉</t>
+          <t>株式会社R-NEXT(アールネクスト)</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>〒285-0005 千葉県佐倉市宮前3-13-1</t>
+          <t>〒277-0005 千葉県柏市柏2-8-17</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>043-486-8500</t>
+          <t>04-7192-6791</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>https://www.daiichi-sakura.com/</t>
+          <t>http://r-kashiwa.co.jp/</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（公開募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -1205,7 +1267,7 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>佐倉・四街道・成田・酒々井の地域密着。売買・賃貸・賃貸管理+リフォーム相談。新築相談も対応</t>
+          <t>柏の地域密着。賃貸・売買・賃貸不動産管理・リフォーム・便利屋。内装リフォーム自社対応</t>
         </is>
       </c>
     </row>
@@ -1215,27 +1277,27 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>丸一土地建物株式会社</t>
+          <t>株式会社第一ホーム佐倉</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>千葉県千葉市中央区本町2-3-17</t>
+          <t>〒285-0005 千葉県佐倉市宮前3-13-1</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>043-222-1411</t>
+          <t>043-486-8500</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>https://www.maruichi-land.co.jp/</t>
+          <t>https://www.daiichi-sakura.com/</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（公開募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
@@ -1245,7 +1307,7 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>昭和27年創業の千葉市地場。不動産売買・賃貸仲介・賃貸管理+リフォーム対応。CPM(米国不動産経営管理士)在籍。社名は土地建物だが不動産業(建設会社ではない)</t>
+          <t>佐倉・四街道・成田・酒々井の地域密着。売買・賃貸・賃貸管理+リフォーム相談。新築相談も対応</t>
         </is>
       </c>
     </row>
@@ -1255,27 +1317,27 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>株式会社もとゆき</t>
+          <t>丸一土地建物株式会社</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>千葉県浦安市北栄1-12-25</t>
+          <t>千葉県千葉市中央区本町2-3-17</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>047-351-1511</t>
+          <t>043-224-6561</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>https://www.motoyuki.jp/</t>
+          <t>https://www.maruichi-land.co.jp/</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（公開募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
@@ -1285,7 +1347,7 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>昭和55年設立・浦安地場。賃貸仲介・賃貸管理。グループの(株)ファーストジョイがリフォーム・メンテナンス・建築設計を担当(=リフォーム部相当)</t>
+          <t>昭和27年創業の千葉市地場。不動産売買・賃貸仲介・賃貸管理+リフォーム対応。CPM(米国不動産経営管理士)在籍。社名は土地建物だが不動産業(建設会社ではない) ※積水ハウス賃貸(シャーメゾン)FC加盟</t>
         </is>
       </c>
     </row>
@@ -1295,27 +1357,27 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>センチュリー21ベルエステート株式会社</t>
+          <t>株式会社もとゆき</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>〒292-0057 千葉県木更津市東中央3-2-13</t>
+          <t>千葉県浦安市北栄1-12-25</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>0438-23-0021</t>
+          <t>047-351-1511</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>https://www.c21bell.co.jp/</t>
+          <t>https://www.motoyuki.jp/</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（自社HPに募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
@@ -1325,7 +1387,7 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>木更津で創業30年超・管理1,300戸超の地場。入居管理～建物管理をワンストップ+リフォーム提案・見積。C21加盟の独立系</t>
+          <t>昭和55年設立・浦安地場。賃貸仲介・賃貸管理。グループの(株)ファーストジョイがリフォーム・メンテナンス・建築設計を担当(=リフォーム部相当)</t>
         </is>
       </c>
     </row>
@@ -1335,27 +1397,27 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>株式会社市川住宅管理</t>
+          <t>センチュリー21ベルエステート株式会社</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>〒272-0143 千葉県市川市相之川4-18-1</t>
+          <t>〒292-0057 千葉県木更津市東中央3-2-13</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>047-399-7070</t>
+          <t>0438-23-0021</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>https://www.ichijyu.jp/</t>
+          <t>https://www.c21bell.co.jp/</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（自社HPに募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
@@ -1365,7 +1427,7 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>市川・浦安の地域密着。賃貸管理+リフォーム/リノベ/メンテ(専用窓口047-702-8635)。リフォーム工事を自社対応</t>
+          <t>木更津で創業30年超・管理1,300戸超の地場。入居管理～建物管理をワンストップ+リフォーム提案・見積。C21加盟の独立系</t>
         </is>
       </c>
     </row>
@@ -1375,42 +1437,82 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
+          <t>株式会社市川住宅管理</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>〒272-0143 千葉県市川市相之川4-18-1</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>047-399-7070</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ichijyu.jp/</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>無（自社HPに募集ページ確認できず）</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>市川・浦安の地域密着。賃貸管理+リフォーム/リノベ/メンテ(専用窓口047-702-8635)。リフォーム工事を自社対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
           <t>株式会社吉岡地所</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>千葉県松戸市南花島中町250-3</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>047-703-3333</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>https://www.yoshiokajisho.com/</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>有(外部紹介型)</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>無（公開募集ページなし／リフォームは外部協力会社に発注=直接打診の好機）</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>東松戸の地域密着。賃貸仲介・売買・賃貸管理が主+内装/インテリア対応。リフォームは協力会社/リフォーム会社を紹介する形=協力会社を活用するタイプ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H18"/>
+  <autoFilter ref="A1:H19"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -1429,6 +1531,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1440,7 +1543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1521,7 +1624,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（公開募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
@@ -1551,7 +1654,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>029-851-5181</t>
+          <t>029-852-6611</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
@@ -1561,7 +1664,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（自社HPに募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
@@ -1571,7 +1674,7 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>つくば地場大手。販売・仲介・賃貸管理(ISSEI賃貸管理)・リフォーム・資産運用。賃貸管理士138名。建設系グループ会社は確認されず</t>
+          <t>つくば地場大手。販売・仲介・賃貸管理(ISSEI賃貸管理)・リフォーム・資産運用。賃貸管理士138名。建設系グループ会社は確認されず ※オーナー/不動産会社向け窓口029-869-5377</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1704,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（自社HPに募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -1611,7 +1714,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>昭和56年設立・水戸中心に約20店舗の茨城地場大手。売買・賃貸・賃貸管理+リフォーム提案・空き家管理。東京/千葉にも支社</t>
+          <t>昭和56年設立・水戸中心に約20店舗の茨城地場大手。売買・賃貸・賃貸管理+リフォーム提案・空き家管理。東京/千葉にも支社 ※県内唯一の東証スタンダード上場(地場発の準大手)</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1734,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>0294-52-3700</t>
+          <t>0294-53-5878</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -1641,7 +1744,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（自社HPに募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -1671,7 +1774,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>029-309-7900</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -1681,7 +1784,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（公開募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1721,7 +1824,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（公開募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -1761,7 +1864,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（公開募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1801,7 +1904,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（公開募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
@@ -1841,7 +1944,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（公開募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -1881,7 +1984,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（公開募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -1921,7 +2024,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（公開募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1961,7 +2064,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（公開募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -2001,7 +2104,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（公開募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
@@ -2041,7 +2144,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（公開募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
@@ -2061,27 +2164,27 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>株式会社GMC</t>
+          <t>有限会社豊成管理システム</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>茨城県結城市大字鹿窪254-5</t>
+          <t>茨城県神栖市奥野谷8168 豊成ビル1F</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>0299-97-0800</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>https://www.gmc-fudousan.com/</t>
+          <t>https://www.housei.net/</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（公開募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
@@ -2091,7 +2194,7 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>2016創業・結城/筑西の地域密着。売買が主だが賃貸管理・リフォーム・リノベ相談も対応。管理規模は要確認</t>
+          <t>神栖・鹿嶋・銚子で不動産30年超。賃貸管理・仲介(年間2,900室紹介)。社名通り管理主体。リフォーム部の有無は要確認</t>
         </is>
       </c>
     </row>
@@ -2101,27 +2204,27 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>有限会社豊成管理システム</t>
+          <t>株式会社スミカ</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>茨城県神栖市奥野谷8168 豊成ビル1F</t>
+          <t>茨城県水戸市元吉田町1847-16 グロリー21-103</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>0299-97-0800</t>
+          <t>029-284-1819</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>https://www.housei.net/</t>
+          <t>https://sumika.link/</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（公開募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
@@ -2131,52 +2234,12 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>神栖・鹿嶋・銚子で不動産30年超。賃貸管理・仲介(年間2,900室紹介)。社名通り管理主体。リフォーム部の有無は要確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>株式会社スミカ</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>茨城県水戸市元吉田町1847-16 グロリー21-103</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>https://sumika.link/</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>要確認（公式HP）</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>水戸の地場。賃貸管理業務+リフォーム対応・売買。売買色が強くリフォーム部の規模は要確認</t>
+          <t>水戸の地場。賃貸管理業務+リフォーム対応・売買。売買色が強くリフォーム部の規模は要確認 ※「不動産売買のプロ」を掲げ売買色が濃い</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H18"/>
+  <autoFilter ref="A1:H17"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -2194,7 +2257,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2206,7 +2268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2267,27 +2329,27 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>吉田不動産株式会社</t>
+          <t>株式会社フレンドホーム</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>埼玉県さいたま市大宮区土手町2-15(本社)</t>
+          <t>埼玉県幸手市東2-8-6</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>048-645-1234</t>
+          <t>0480-43-0021</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>https://www.yoshida-re.co.jp/</t>
+          <t>https://friend-home.jp/</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（自社HPに募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
@@ -2297,7 +2359,7 @@
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>本社大宮。管理約7,256戸。リフォーム・原状回復・大規模修繕・分割施工。市川/船橋/浦安/松戸(東西線)中心の地域密着。建設系グループなし</t>
+          <t>1988設立。賃貸管理+リフォーム(水まわり・増改築・外壁・屋根・リノベ)のワンストップ。owner/reform専用サイトあり。建設系グループなし ※センチュリー21加盟</t>
         </is>
       </c>
     </row>
@@ -2307,27 +2369,27 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>株式会社フレンドホーム</t>
+          <t>株式会社大和不動産</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>埼玉県幸手市東2-8-6</t>
+          <t>埼玉県さいたま市浦和区(浦和店 048-824-1161)</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>0480-43-0021</t>
+          <t>048-824-1161</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>https://friend-home.jp/</t>
+          <t>https://www.saitama-chintai.jp/</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（自社HPに募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
@@ -2337,7 +2399,7 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>1988設立。賃貸管理+リフォーム(水まわり・増改築・外壁・屋根・リノベ)のワンストップ。owner/reform専用サイトあり。建設系グループなし</t>
+          <t>昭和27年創業の浦和地場。賃貸仲介・売買・賃貸管理(約9,500室・駐車場5,000台)。リフォーム・相続解決のグループ会社あり(建設会社ではない)</t>
         </is>
       </c>
     </row>
@@ -2347,27 +2409,27 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>松堀不動産株式会社</t>
+          <t>有限会社サカイ・エージェンシー</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>埼玉県東松山市八木町2-3-2</t>
+          <t>〒360-0845 埼玉県熊谷市美土里町2-188-1</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>0493-22-0788</t>
+          <t>048-533-2230</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>https://www.matsubori.co.jp/</t>
+          <t>https://sakai-ag.com/</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>有 https://sakai-ag.com/partner/（改修・リノベ施工/退去清掃・メンテ/引越の協力事業者を募集）</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -2377,7 +2439,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>管理約5,580戸。リフォーム・外壁塗装。松堀トラストHD傘下(松堀不動産=賃貸管理/松堀不動産販売=売買/アルイエ=買取)。建設・工務店なし。自社で建設業許可保有(=リフォーム内製)だが工務店グループは無し</t>
+          <t>1994設立・熊谷/深谷の賃貸管理に強い地場。管理約300戸入居率98.2%。賃貸管理・仲介・売買+大規模修繕提案・空室対策</t>
         </is>
       </c>
     </row>
@@ -2387,37 +2449,37 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>株式会社大和不動産</t>
+          <t>マルヤ住宅株式会社</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>埼玉県さいたま市浦和区(浦和店 048-824-1161)</t>
+          <t>埼玉県春日部市中央1-1-5</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>048-824-1161</t>
+          <t>048-761-3737</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>https://www.saitama-chintai.jp/</t>
+          <t>https://www.maruya-jutaku.co.jp/</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>無（公開募集ページ確認できず）</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>昭和27年創業の浦和地場。賃貸仲介・売買・賃貸管理(約9,500室・駐車場5,000台)。リフォーム・相続解決のグループ会社あり(建設会社ではない)</t>
+          <t>1966創業。リフォーム+賃貸管理。マルヤ住宅販売(売買部門)あり=建設会社ではない</t>
         </is>
       </c>
     </row>
@@ -2427,27 +2489,27 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>マルヤ住宅株式会社</t>
+          <t>松堀不動産株式会社</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>埼玉県春日部市中央1-1-5</t>
+          <t>埼玉県東松山市箭弓町2-3-2</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>048-761-3737</t>
+          <t>0493-24-1111</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>https://www.maruya-jutaku.co.jp/</t>
+          <t>https://www.matsubori.co.jp/</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（自社HPに募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -2457,7 +2519,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>1966創業。リフォーム+賃貸管理。マルヤ住宅販売(売買部門)あり=建設会社ではない</t>
+          <t>管理約5,580戸。リフォーム・外壁塗装。松堀トラストHD傘下(松堀不動産=賃貸管理/松堀不動産販売=売買/アルイエ=買取)。建設・工務店なし。自社で建設業許可保有(=リフォーム内製)だが工務店グループは無し ※定款に土木・建築工事の設計施工請負あり(=自社施工力大)→純粋な管理特化ではない点に留意</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2549,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（自社HPに募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -2527,7 +2589,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（公開募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -2567,7 +2629,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（自社HPに募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
@@ -2607,7 +2669,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（公開募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -2647,7 +2709,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（自社HPに募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -2667,27 +2729,27 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>有限会社サカイ・エージェンシー</t>
+          <t>株式会社別所不動産</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>〒360-0845 埼玉県熊谷市美土里町2-188-1</t>
+          <t>〒336-0027 埼玉県さいたま市南区沼影1-8-22</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>048-533-2230</t>
+          <t>048-861-3333</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>https://sakai-ag.com/</t>
+          <t>https://www.bessyo.co.jp/</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（公開募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -2697,7 +2759,7 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>1994設立・熊谷/深谷の賃貸管理に強い地場。管理約300戸入居率98.2%。賃貸管理・仲介・売買+大規模修繕提案・空室対策</t>
+          <t>創立56年・さいたま市南区の地元密着。賃貸管理業務+リフォーム提案で入居率UP支援。建設系グループなし</t>
         </is>
       </c>
     </row>
@@ -2707,27 +2769,27 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>株式会社別所不動産</t>
+          <t>株式会社ワンステップハウス</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>〒336-0027 埼玉県さいたま市南区沼影1-8-22</t>
+          <t>埼玉県さいたま市大宮区桜木町1-1-11 棚沢ビル2F</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>048-861-3333</t>
+          <t>048-650-3100</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>https://www.bessyo.co.jp/</t>
+          <t>https://www.onestephouse.co.jp/</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（公開募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -2737,7 +2799,7 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>創立56年・さいたま市南区の地元密着。賃貸管理業務+リフォーム提案で入居率UP支援。建設系グループなし</t>
+          <t>さいたま市の賃貸仲介・入居管理・リフォーム・売却をワンストップ。退去後オーナーにリフォーム提案。リフォーム実績ページあり</t>
         </is>
       </c>
     </row>
@@ -2747,27 +2809,27 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>株式会社ワンステップハウス</t>
+          <t>有限会社アプリ</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>埼玉県さいたま市大宮区(大宮西口/東口/南浦和店)</t>
+          <t>埼玉県川越市中原町2-10-2</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>049-228-5222</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>https://www.onestephouse.co.jp/</t>
+          <t>https://www.appri-kawagoe.com/</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（公開募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
@@ -2777,7 +2839,7 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>さいたま市の賃貸仲介・入居管理・リフォーム・売却をワンストップ。退去後オーナーにリフォーム提案。リフォーム実績ページあり</t>
+          <t>川越の賃貸管理・満室経営・空室対策に注力+リフォーム対応。注文住宅も扱う点は要確認。川越市駅3分</t>
         </is>
       </c>
     </row>
@@ -2787,27 +2849,27 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>有限会社アプリ</t>
+          <t>株式会社末広不動産</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>埼玉県川越市中原町2-10-2</t>
+          <t>〒360-0037 埼玉県熊谷市筑波2-14</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>049-228-5222</t>
+          <t>048-522-1112</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>https://www.appri-kawagoe.com/</t>
+          <t>https://www.suehiro-re.co.jp/</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>要確認（公式HP）</t>
+          <t>無（公開募集ページ確認できず）</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
@@ -2817,52 +2879,12 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>川越の賃貸管理・満室経営・空室対策に注力+リフォーム対応。注文住宅も扱う点は要確認。川越市駅3分</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>株式会社末広不動産</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>〒360-0037 埼玉県熊谷市筑波2-14</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>048-522-1112</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>https://www.suehiro-re.co.jp/</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>要確認（公式HP）</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
           <t>熊谷駅2分の地場。不動産売買・賃貸・賃貸管理業務+リフォーム対応</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H16"/>
+  <autoFilter ref="A1:H15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -2878,7 +2900,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
